--- a/Prompts/conditions.xlsx
+++ b/Prompts/conditions.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Conditions'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Conditions'!$A$1:$E$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,13 +444,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1777,8 +1777,1736 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Q17a</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Q10d</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Q23a</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Q28a</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Q36a</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E49"/>
+  <autoFilter ref="A1:E113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2679,7 +4407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2706,7 +4434,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>C1 to C6 = language x persona (2 x 3)</t>
+          <t>C1 to C14 = language x persona (2 x 7). C1 to C6 are the original DE/EN x none/Germany/US. C7 to C14 add Austria, Switzerland, Australia, Canada in both languages</t>
         </is>
       </c>
     </row>
@@ -2742,7 +4470,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>none = no persona, Germany = person living in Germany, US = person living in the United States</t>
+          <t>none = no persona. Otherwise a person living in that country: Germany, Austria, Switzerland (German speaking), US, Australia, Canada (English speaking). Each country is asked in DE and EN</t>
         </is>
       </c>
     </row>
@@ -2766,7 +4494,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6 conditions x 8 items = 48 base prompts per model</t>
+          <t>14 conditions x 8 items = 112 base prompts per model (official option order). build_prompts.py adds order variants, so prompts.csv has 224 prompts per model</t>
         </is>
       </c>
     </row>
@@ -2779,6 +4507,18 @@
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Exact wording copied from DE24 and US24 questionnaires. Neutral stem column is filled only for Q34 and Q28a. Blank means use the official stem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Option order</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>official = official order, prompt_id C2_Q17a_T1. rev = reversed order, only ordinal items (5), prompt_id ends with _rev. shuf1 = one fixed shuffled order, only nominal items (3), prompt_id ends with _shuf1. The shuffle is the same in every condition. letter_to_original in prompts.csv maps answers back to the official order</t>
         </is>
       </c>
     </row>
